--- a/data/availability/projects/dorra/village-west.xlsx
+++ b/data/availability/projects/dorra/village-west.xlsx
@@ -587,7 +587,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -637,7 +637,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -737,7 +737,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Delivery 2028 (+ Nanny)</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -837,7 +837,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1237,7 +1237,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Delivery 2029 (+ Nanny)</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1337,7 +1337,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -1387,7 +1387,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1587,7 +1587,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1637,7 +1637,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -1787,7 +1787,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -1909,7 +1909,6 @@
       <c r="G2" t="n">
         <v>89</v>
       </c>
-      <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -1920,7 +1919,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -1966,7 +1965,6 @@
       <c r="G3" t="n">
         <v>123</v>
       </c>
-      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -1977,7 +1975,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -2023,7 +2021,6 @@
       <c r="G4" t="n">
         <v>130</v>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -2034,7 +2031,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -2080,7 +2077,6 @@
       <c r="G5" t="n">
         <v>149</v>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -2091,7 +2087,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -2137,7 +2133,6 @@
       <c r="G6" t="n">
         <v>159</v>
       </c>
-      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -2148,7 +2143,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -2194,7 +2189,6 @@
       <c r="G7" t="n">
         <v>163</v>
       </c>
-      <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -2205,7 +2199,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -2251,7 +2245,6 @@
       <c r="G8" t="n">
         <v>164</v>
       </c>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -2262,7 +2255,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -2308,7 +2301,6 @@
       <c r="G9" t="n">
         <v>167</v>
       </c>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -2319,7 +2311,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2365,7 +2357,6 @@
       <c r="G10" t="n">
         <v>169</v>
       </c>
-      <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -2376,7 +2367,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Delivery 2028 (+ Nanny)</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -2422,7 +2413,6 @@
       <c r="G11" t="n">
         <v>175</v>
       </c>
-      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -2433,7 +2423,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Delivery 2028 (+ Nanny)</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -2479,7 +2469,6 @@
       <c r="G12" t="n">
         <v>203</v>
       </c>
-      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -2490,7 +2479,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -2536,7 +2525,6 @@
       <c r="G13" t="n">
         <v>89</v>
       </c>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -2547,7 +2535,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -2593,7 +2581,6 @@
       <c r="G14" t="n">
         <v>95</v>
       </c>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -2604,7 +2591,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -2650,7 +2637,6 @@
       <c r="G15" t="n">
         <v>141</v>
       </c>
-      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -2661,7 +2647,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -2707,7 +2693,6 @@
       <c r="G16" t="n">
         <v>154</v>
       </c>
-      <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -2718,7 +2703,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -2764,7 +2749,6 @@
       <c r="G17" t="n">
         <v>164</v>
       </c>
-      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -2775,7 +2759,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
@@ -2821,7 +2805,6 @@
       <c r="G18" t="n">
         <v>167</v>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -2832,7 +2815,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2878,7 +2861,6 @@
       <c r="G19" t="n">
         <v>177</v>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -2889,7 +2871,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2935,7 +2917,6 @@
       <c r="G20" t="n">
         <v>203</v>
       </c>
-      <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -2946,7 +2927,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
@@ -2992,7 +2973,6 @@
       <c r="G21" t="n">
         <v>190</v>
       </c>
-      <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -3003,7 +2983,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -3049,7 +3029,6 @@
       <c r="G22" t="n">
         <v>213</v>
       </c>
-      <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -3060,7 +3039,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -3106,7 +3085,6 @@
       <c r="G23" t="n">
         <v>231</v>
       </c>
-      <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -3117,7 +3095,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -3163,7 +3141,6 @@
       <c r="G24" t="n">
         <v>243</v>
       </c>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -3174,7 +3151,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -3220,7 +3197,6 @@
       <c r="G25" t="n">
         <v>75</v>
       </c>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -3231,7 +3207,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -3277,7 +3253,6 @@
       <c r="G26" t="n">
         <v>123</v>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -3288,7 +3263,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -3334,7 +3309,6 @@
       <c r="G27" t="n">
         <v>130</v>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -3345,7 +3319,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -3391,7 +3365,6 @@
       <c r="G28" t="n">
         <v>149</v>
       </c>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -3402,7 +3375,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -3448,7 +3421,6 @@
       <c r="G29" t="n">
         <v>154</v>
       </c>
-      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -3459,7 +3431,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -3505,7 +3477,6 @@
       <c r="G30" t="n">
         <v>159</v>
       </c>
-      <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -3516,7 +3487,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -3562,7 +3533,6 @@
       <c r="G31" t="n">
         <v>163</v>
       </c>
-      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -3573,7 +3543,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3619,7 +3589,6 @@
       <c r="G32" t="n">
         <v>164</v>
       </c>
-      <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -3630,7 +3599,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
@@ -3676,7 +3645,6 @@
       <c r="G33" t="n">
         <v>167</v>
       </c>
-      <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -3687,7 +3655,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3733,7 +3701,6 @@
       <c r="G34" t="n">
         <v>175</v>
       </c>
-      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -3744,7 +3711,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Delivery 2029 (+ Nanny)</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3790,7 +3757,6 @@
       <c r="G35" t="n">
         <v>203</v>
       </c>
-      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -3801,7 +3767,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3847,7 +3813,6 @@
       <c r="G36" t="n">
         <v>65</v>
       </c>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -3858,7 +3823,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3904,7 +3869,6 @@
       <c r="G37" t="n">
         <v>95</v>
       </c>
-      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -3915,7 +3879,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3961,7 +3925,6 @@
       <c r="G38" t="n">
         <v>123</v>
       </c>
-      <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -3972,7 +3935,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -4018,7 +3981,6 @@
       <c r="G39" t="n">
         <v>141</v>
       </c>
-      <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -4029,7 +3991,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -4075,7 +4037,6 @@
       <c r="G40" t="n">
         <v>149</v>
       </c>
-      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -4086,7 +4047,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4132,7 +4093,6 @@
       <c r="G41" t="n">
         <v>164</v>
       </c>
-      <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -4143,7 +4103,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -4189,7 +4149,6 @@
       <c r="G42" t="n">
         <v>167</v>
       </c>
-      <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -4200,7 +4159,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4246,7 +4205,6 @@
       <c r="G43" t="n">
         <v>190</v>
       </c>
-      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -4257,7 +4215,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -4303,7 +4261,6 @@
       <c r="G44" t="n">
         <v>203</v>
       </c>
-      <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -4314,7 +4271,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -4360,7 +4317,6 @@
       <c r="G45" t="n">
         <v>190</v>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -4371,7 +4327,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4417,7 +4373,6 @@
       <c r="G46" t="n">
         <v>213</v>
       </c>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -4428,7 +4383,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4474,7 +4429,6 @@
       <c r="G47" t="n">
         <v>231</v>
       </c>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -4485,7 +4439,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4531,7 +4485,6 @@
       <c r="G48" t="n">
         <v>243</v>
       </c>
-      <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -4542,7 +4495,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Delivery 2029</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4564,7 +4517,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4588,7 +4541,6 @@
       <c r="G49" t="n">
         <v>220</v>
       </c>
-      <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -4621,7 +4573,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -4645,7 +4597,6 @@
       <c r="G50" t="n">
         <v>220</v>
       </c>
-      <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -4678,7 +4629,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -4702,7 +4653,6 @@
       <c r="G51" t="n">
         <v>220</v>
       </c>
-      <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -4713,7 +4663,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4735,7 +4685,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Town House</t>
+          <t>Townhouse</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4759,7 +4709,6 @@
       <c r="G52" t="n">
         <v>220</v>
       </c>
-      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -4770,7 +4719,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
@@ -4816,7 +4765,6 @@
       <c r="G53" t="n">
         <v>270</v>
       </c>
-      <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr">
         <is>
           <t>Landscape / Pool View</t>
@@ -4827,7 +4775,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Delivery 2028</t>
+          <t>Ready to Move (RTM)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
